--- a/data/output/stats.xlsx
+++ b/data/output/stats.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$H$2</definedName>
@@ -24,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Winter 2026 Game 1'!$A$1:$Q$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Winter 2026 Game 2'!$A$1:$Q$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cyclo Winter 2026 Game 3'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cyclo Winter 2026 Game 4'!$A$1:$Q$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -816,29 +818,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.628</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>0.633</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>0.920</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.553</t>
         </is>
       </c>
     </row>
@@ -970,59 +972,59 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.600</t>
+          <t>1.538</t>
         </is>
       </c>
     </row>
@@ -1033,25 +1035,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -1063,29 +1065,29 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.154</t>
         </is>
       </c>
     </row>
@@ -1096,16 +1098,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
         <v>6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -1129,26 +1131,26 @@
         <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.818</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.818</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.273</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.428</t>
+          <t>2.091</t>
         </is>
       </c>
     </row>
@@ -1159,17 +1161,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
@@ -1189,29 +1191,29 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.091</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.857</t>
+          <t>1.727</t>
         </is>
       </c>
     </row>
@@ -1222,16 +1224,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -1252,29 +1254,29 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.357</t>
         </is>
       </c>
     </row>
@@ -1285,19 +1287,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1318,26 +1320,26 @@
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>1.181</t>
         </is>
       </c>
     </row>
@@ -1348,17 +1350,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
@@ -1378,29 +1380,29 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.083</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>1.833</t>
         </is>
       </c>
     </row>
@@ -1411,17 +1413,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
       <c r="F9" t="n">
         <v>3</v>
       </c>
@@ -1441,29 +1443,29 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.437</t>
         </is>
       </c>
     </row>
@@ -1474,10 +1476,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -1498,35 +1500,35 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.800</t>
         </is>
       </c>
     </row>
@@ -1726,16 +1728,16 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" t="n">
         <v>6</v>
       </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1756,29 +1758,29 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -1911,59 +1913,59 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.600</t>
+          <t>1.538</t>
         </is>
       </c>
     </row>
@@ -1974,25 +1976,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -2004,29 +2006,29 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.154</t>
         </is>
       </c>
     </row>
@@ -2037,16 +2039,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
         <v>6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -2070,26 +2072,26 @@
         <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.818</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.818</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.273</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.428</t>
+          <t>2.091</t>
         </is>
       </c>
     </row>
@@ -2100,17 +2102,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
@@ -2130,29 +2132,29 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.091</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.857</t>
+          <t>1.727</t>
         </is>
       </c>
     </row>
@@ -2163,16 +2165,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -2193,29 +2195,29 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.357</t>
         </is>
       </c>
     </row>
@@ -2226,19 +2228,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2259,26 +2261,26 @@
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>1.181</t>
         </is>
       </c>
     </row>
@@ -2289,17 +2291,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
@@ -2319,29 +2321,29 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.083</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>1.833</t>
         </is>
       </c>
     </row>
@@ -2352,17 +2354,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
       <c r="F9" t="n">
         <v>3</v>
       </c>
@@ -2382,29 +2384,29 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.437</t>
         </is>
       </c>
     </row>
@@ -2415,10 +2417,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -2439,35 +2441,35 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.800</t>
         </is>
       </c>
     </row>
@@ -2667,16 +2669,16 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" t="n">
         <v>6</v>
       </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2697,29 +2699,29 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -2730,59 +2732,59 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.628</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>0.633</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>0.920</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.553</t>
         </is>
       </c>
     </row>
@@ -2915,59 +2917,59 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.643</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.600</t>
+          <t>1.489</t>
         </is>
       </c>
     </row>
@@ -2978,25 +2980,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -3008,29 +3010,29 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.733</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.600</t>
+          <t>2.195</t>
         </is>
       </c>
     </row>
@@ -3041,16 +3043,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
         <v>6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -3074,11 +3076,11 @@
         <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.818</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -3088,12 +3090,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.273</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.321</t>
+          <t>2.023</t>
         </is>
       </c>
     </row>
@@ -3104,17 +3106,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
@@ -3134,29 +3136,29 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.091</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.911</t>
+          <t>1.758</t>
         </is>
       </c>
     </row>
@@ -3167,16 +3169,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -3197,14 +3199,14 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -3214,12 +3216,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.386</t>
         </is>
       </c>
     </row>
@@ -3230,19 +3232,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3263,26 +3265,26 @@
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>1.219</t>
         </is>
       </c>
     </row>
@@ -3293,17 +3295,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
@@ -3323,29 +3325,29 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.083</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>1.833</t>
         </is>
       </c>
     </row>
@@ -3356,17 +3358,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
       <c r="F9" t="n">
         <v>3</v>
       </c>
@@ -3386,29 +3388,29 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.437</t>
         </is>
       </c>
     </row>
@@ -3419,10 +3421,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -3443,35 +3445,35 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.733</t>
         </is>
       </c>
     </row>
@@ -3671,16 +3673,16 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" t="n">
         <v>6</v>
       </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -3701,29 +3703,29 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>0.727</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
           <t>0.667</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1.394</t>
         </is>
       </c>
     </row>
@@ -3734,59 +3736,59 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.628</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>0.633</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>0.920</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.553</t>
         </is>
       </c>
     </row>
@@ -6491,4 +6493,819 @@
   <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.200</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3.200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kunal</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.800</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.800</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.800</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.600</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0.833</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/output/stats.xlsx
+++ b/data/output/stats.xlsx
@@ -1,31 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="League Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Total" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Legend" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="League Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Player Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cyclo Total" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cyclo Winter 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cyclo Winter 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cyclo Winter 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cyclo Winter 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cyclo Winter 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cyclo Winter 2026 Game 5" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Cyclo Winter 2026 Game 6" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cyclo Total'!$A$1:$Q$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cyclo Winter 2026 Total'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cyclo Total'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cyclo Winter 2026 Total'!$A$1:$Q$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Winter 2026 Game 1'!$A$1:$Q$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Winter 2026 Game 2'!$A$1:$Q$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cyclo Winter 2026 Game 3'!$A$1:$Q$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cyclo Winter 2026 Game 4'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Winter 2026 Game 5'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Winter 2026 Game 6'!$A$1:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -745,118 +749,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>League</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Games Played</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Players</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Team BA</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Team OBP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Team SLG</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Team OPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Fray</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Cyclones</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.628</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.633</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.920</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1.553</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -972,19 +872,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -996,67 +896,67 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1065,124 +965,124 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.154</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1191,61 +1091,61 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.727</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1254,49 +1154,49 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>1.400</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1308,64 +1208,64 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1380,52 +1280,52 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1443,49 +1343,49 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.437</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Rich</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1494,310 +1394,184 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.900</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Ramos</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.286</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.286</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0.286</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.572</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2.200</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>11</v>
-      </c>
-      <c r="C14" t="n">
-        <v>9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6</v>
-      </c>
-      <c r="E14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.334</t>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0.607</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.607</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0.964</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1.571</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF0000FF"/>
+    <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1913,19 +1687,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1937,35 +1711,35 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -1976,28 +1750,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2006,29 +1780,29 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.154</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
@@ -2039,59 +1813,59 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
@@ -2102,28 +1876,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2132,29 +1906,29 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.727</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
@@ -2165,28 +1939,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -2195,29 +1969,29 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -2228,19 +2002,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2255,32 +2029,32 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -2291,25 +2065,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2321,29 +2095,29 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>3.500</t>
         </is>
       </c>
     </row>
@@ -2354,19 +2128,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2384,29 +2158,29 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.437</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -2417,16 +2191,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -2438,38 +2212,38 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -2480,59 +2254,59 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>7</v>
-      </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>4.000</t>
         </is>
       </c>
     </row>
@@ -2543,16 +2317,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2564,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2576,26 +2350,26 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -2606,202 +2380,243 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="I15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2.200</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>11</v>
-      </c>
-      <c r="C14" t="n">
-        <v>9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6</v>
-      </c>
-      <c r="E14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.334</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TEAM TOTALS</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0.628</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0.633</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0.920</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1.553</t>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0.696</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.696</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>1.348</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>2.044</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF00FF00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>League</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Games Played</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total Players</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Team BA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Team OBP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Team SLG</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Team OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fray</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cyclones</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.633</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.644</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.979</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.623</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2917,19 +2732,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2950,58 +2765,58 @@
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.471</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -3010,53 +2825,53 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.195</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
         <v>11</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>9</v>
       </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -3064,70 +2879,70 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0.733</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.733</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.023</t>
+          <t>2.266</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3136,121 +2951,121 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.758</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>2.231</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -3259,64 +3074,64 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.615</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
         <v>9</v>
       </c>
-      <c r="E8" t="n">
-        <v>7</v>
-      </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3325,175 +3140,175 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.471</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
         <v>7</v>
       </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6</v>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.437</t>
+          <t>1.285</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>14</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>1.286</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>2.072</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="n">
         <v>10</v>
-      </c>
-      <c r="C11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -3502,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -3514,52 +3329,52 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.917</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>1.542</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3577,124 +3392,124 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>0.888</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
         <v>9</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
         <v>6</v>
       </c>
-      <c r="E14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3703,97 +3518,2798 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M14" t="n">
         <v>6</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ramos</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rich</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>0.667</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0000FF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.647</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.647</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.471</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1.533</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.266</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.846</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.846</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1.385</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.231</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.615</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.647</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.647</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.471</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.714</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kunal</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.286</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2.072</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.917</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.542</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ramos</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rich</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0.633</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.644</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0.979</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1.623</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF00FF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.647</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.611</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.435</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.765</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1.533</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.298</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.846</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1.385</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.171</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.643</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.643</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.647</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.491</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.714</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.339</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kunal</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.286</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2.072</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.917</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.542</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.455</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.899</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ramos</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.400</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.650</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rich</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>0.727</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>0.667</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>1.394</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G16" s="2" t="n">
+      <c r="B20" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0.628</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0.633</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0.920</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1.553</t>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.644</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0.979</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1.623</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/output/stats.xlsx
+++ b/data/output/stats.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Cyclo Winter 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Cyclo Winter 2026 Game 5" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Cyclo Winter 2026 Game 6" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Cyclo Winter 2026 Game 7" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$H$2</definedName>
@@ -30,6 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cyclo Winter 2026 Game 4'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Winter 2026 Game 5'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Winter 2026 Game 6'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Winter 2026 Game 7'!$A$1:$Q$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2505,6 +2507,884 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.667</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kunal</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1.333</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ramos</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.333</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.333</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.250</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0.559</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.559</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1.029</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1.588</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2578,29 +3458,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>0.622</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.634</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>0.986</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>1.620</t>
         </is>
       </c>
     </row>
@@ -2732,19 +3612,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2765,26 +3645,26 @@
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.850</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -2858,13 +3738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="n">
         <v>17</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -2876,10 +3756,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2888,29 +3768,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.266</t>
+          <t>2.294</t>
         </is>
       </c>
     </row>
@@ -2984,19 +3864,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -3017,26 +3897,26 @@
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.231</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -3047,16 +3927,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -3077,29 +3957,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.437</t>
         </is>
       </c>
     </row>
@@ -3110,59 +3990,59 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>9</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8</v>
-      </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1.477</t>
         </is>
       </c>
     </row>
@@ -3173,19 +4053,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -3203,29 +4083,29 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
         <v>7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.941</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
@@ -3236,59 +4116,59 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
         <v>11</v>
       </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>9</v>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.176</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.072</t>
+          <t>1.941</t>
         </is>
       </c>
     </row>
@@ -3488,13 +4368,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -3506,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3518,29 +4398,29 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.778</t>
         </is>
       </c>
     </row>
@@ -3551,13 +4431,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -3566,13 +4446,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -3584,26 +4464,26 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.728</t>
         </is>
       </c>
     </row>
@@ -3677,59 +4557,59 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9</v>
+      </c>
+      <c r="M17" t="n">
         <v>6</v>
       </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.231</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.846</t>
         </is>
       </c>
     </row>
@@ -3740,19 +4620,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3770,29 +4650,29 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.307</t>
         </is>
       </c>
     </row>
@@ -3925,19 +4805,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3958,26 +4838,26 @@
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.850</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -4051,13 +4931,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="n">
         <v>17</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -4069,10 +4949,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4081,29 +4961,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.266</t>
+          <t>2.294</t>
         </is>
       </c>
     </row>
@@ -4177,19 +5057,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -4210,26 +5090,26 @@
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.231</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -4240,16 +5120,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -4270,29 +5150,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.437</t>
         </is>
       </c>
     </row>
@@ -4303,59 +5183,59 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>9</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8</v>
-      </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1.477</t>
         </is>
       </c>
     </row>
@@ -4366,19 +5246,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4396,29 +5276,29 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
         <v>7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.941</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
@@ -4429,59 +5309,59 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
         <v>11</v>
       </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>9</v>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.176</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.072</t>
+          <t>1.941</t>
         </is>
       </c>
     </row>
@@ -4681,13 +5561,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -4699,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -4711,29 +5591,29 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.778</t>
         </is>
       </c>
     </row>
@@ -4744,13 +5624,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -4759,13 +5639,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4777,26 +5657,26 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.728</t>
         </is>
       </c>
     </row>
@@ -4870,59 +5750,59 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9</v>
+      </c>
+      <c r="M17" t="n">
         <v>6</v>
       </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.231</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.846</t>
         </is>
       </c>
     </row>
@@ -4933,19 +5813,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -4963,29 +5843,29 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.307</t>
         </is>
       </c>
     </row>
@@ -4996,28 +5876,28 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>3</v>
@@ -5026,29 +5906,29 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>0.622</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.634</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>0.986</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>1.620</t>
         </is>
       </c>
     </row>
@@ -5181,19 +6061,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -5214,26 +6094,26 @@
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.619</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.850</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
@@ -5307,13 +6187,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="n">
         <v>17</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -5325,10 +6205,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -5337,29 +6217,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.298</t>
+          <t>2.338</t>
         </is>
       </c>
     </row>
@@ -5433,19 +6313,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -5466,26 +6346,26 @@
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.171</t>
+          <t>1.956</t>
         </is>
       </c>
     </row>
@@ -5496,16 +6376,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -5526,29 +6406,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>0.588</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.643</t>
+          <t>1.463</t>
         </is>
       </c>
     </row>
@@ -5559,59 +6439,59 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>9</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8</v>
-      </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.492</t>
         </is>
       </c>
     </row>
@@ -5622,19 +6502,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5652,29 +6532,29 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
         <v>7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.684</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.941</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>1.625</t>
         </is>
       </c>
     </row>
@@ -5685,59 +6565,59 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
         <v>11</v>
       </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>9</v>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.176</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.072</t>
+          <t>1.941</t>
         </is>
       </c>
     </row>
@@ -5937,13 +6817,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -5955,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -5967,29 +6847,29 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.778</t>
         </is>
       </c>
     </row>
@@ -6000,13 +6880,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -6015,13 +6895,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -6033,26 +6913,26 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>0.884</t>
         </is>
       </c>
     </row>
@@ -6126,59 +7006,59 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9</v>
+      </c>
+      <c r="M17" t="n">
         <v>6</v>
       </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.231</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.846</t>
         </is>
       </c>
     </row>
@@ -6189,19 +7069,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -6219,29 +7099,29 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>0.667</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0.727</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1.359</t>
         </is>
       </c>
     </row>
@@ -6252,28 +7132,28 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>3</v>
@@ -6282,29 +7162,29 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>0.622</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.634</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>0.986</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>1.620</t>
         </is>
       </c>
     </row>

--- a/data/output/stats.xlsx
+++ b/data/output/stats.xlsx
@@ -22,11 +22,12 @@
     <sheet name="Cyclo Spring 2026 Total" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Cyclo Spring 2026 Game 1" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Cyclo Spring 2026 Game 2" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Cyclo Spring 2026 Game 3" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$H$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cyclo Total'!$A$1:$Q$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cyclo Total'!$A$1:$Q$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cyclo Winter 2026 Total'!$A$1:$Q$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Winter 2026 Game 1'!$A$1:$Q$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Winter 2026 Game 2'!$A$1:$Q$13</definedName>
@@ -35,9 +36,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Winter 2026 Game 5'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Winter 2026 Game 6'!$A$1:$Q$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Winter 2026 Game 7'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cyclo Spring 2026 Total'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cyclo Spring 2026 Total'!$A$1:$Q$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Cyclo Spring 2026 Game 1'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Cyclo Spring 2026 Game 2'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Cyclo Spring 2026 Game 3'!$A$1:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3398,7 +3400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3514,19 +3516,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3541,32 +3543,32 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.875</t>
         </is>
       </c>
     </row>
@@ -3577,17 +3579,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
@@ -3595,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -3607,29 +3609,29 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.166</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -3640,13 +3642,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3658,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -3670,10 +3672,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3687,12 +3689,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>3.167</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3.333</t>
+          <t>4.167</t>
         </is>
       </c>
     </row>
@@ -3703,16 +3705,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -3721,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3733,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3750,12 +3752,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.750</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.750</t>
         </is>
       </c>
     </row>
@@ -3829,10 +3831,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
@@ -3866,22 +3868,22 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.111</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.143</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
@@ -3955,59 +3957,59 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
         <v>5</v>
       </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4</v>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>2.429</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>3.143</t>
         </is>
       </c>
     </row>
@@ -4018,16 +4020,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -4055,42 +4057,42 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>1.090</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -4105,124 +4107,124 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.833</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.200</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.033</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.179</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4234,13 +4236,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -4254,143 +4256,269 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.545</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.545</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.636</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Stephen</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C14" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.429</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0.429</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0.429</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0.858</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TEAM TOTALS</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0.686</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0.676</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1.129</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1.805</t>
+      <c r="G18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0.653</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.646</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>1.214</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1.860</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6151,156 +6279,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>League</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Games Played</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Players</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Team BA</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Team OBP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Team SLG</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Team OPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Fray</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Cyclones</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.637</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.644</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1.021</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1.665</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Fray</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Cyclones</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.637</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.644</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1.021</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.665</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H3"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6416,59 +6402,59 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.962</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -6479,16 +6465,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -6506,32 +6492,32 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>3.500</t>
         </is>
       </c>
     </row>
@@ -6542,19 +6528,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -6563,7 +6549,7 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -6572,49 +6558,49 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.700</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>5.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -6623,7 +6609,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6638,52 +6624,52 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>3.500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -6698,49 +6684,49 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Briana</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -6749,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -6758,102 +6744,102 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.304</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6863,13 +6849,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -6887,61 +6873,61 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -6950,61 +6936,61 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.905</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -7013,52 +6999,52 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7067,67 +7053,67 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.727</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7139,550 +7125,251 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>1.211</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.948</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Kyla</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>32</v>
-      </c>
-      <c r="C14" t="n">
-        <v>32</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19</v>
-      </c>
-      <c r="E14" t="n">
-        <v>14</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>11</v>
-      </c>
-      <c r="M14" t="n">
-        <v>15</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.594</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0.594</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0.812</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.406</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Kyle</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>11</v>
-      </c>
-      <c r="C16" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3</v>
-      </c>
-      <c r="M16" t="n">
-        <v>5</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0.444</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0.444</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0.444</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0.888</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Rafael</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>18</v>
-      </c>
-      <c r="C17" t="n">
-        <v>18</v>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>16</v>
-      </c>
-      <c r="M17" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>1.222</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1.778</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ramos</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>14</v>
-      </c>
-      <c r="C18" t="n">
-        <v>11</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>0.455</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>0.728</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Rich</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="M15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>1.429</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>2.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>20</v>
-      </c>
-      <c r="C20" t="n">
-        <v>20</v>
-      </c>
-      <c r="D20" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>9</v>
-      </c>
-      <c r="M20" t="n">
-        <v>9</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0.550</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0.550</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>0.950</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>15</v>
-      </c>
-      <c r="C21" t="n">
-        <v>13</v>
-      </c>
-      <c r="D21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>7</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>0.692</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1.307</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q21"/>
+  <autoFilter ref="A1:Q13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF0000FF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>League</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Games Played</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total Players</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Team BA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Team OBP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Team SLG</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Team OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fray</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cyclones</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.631</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.638</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.056</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.694</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fray</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cyclones</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.631</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.638</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.056</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.694</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7798,19 +7485,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
         <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -7825,32 +7512,32 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>0.643</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>0.643</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.962</t>
+          <t>0.964</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.607</t>
         </is>
       </c>
     </row>
@@ -7861,17 +7548,17 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
         <v>8</v>
       </c>
-      <c r="C3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
@@ -7879,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -7891,29 +7578,29 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.400</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>2.200</t>
         </is>
       </c>
     </row>
@@ -7924,13 +7611,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C4" t="n">
         <v>23</v>
       </c>
-      <c r="C4" t="n">
-        <v>20</v>
-      </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -7942,7 +7629,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -7954,29 +7641,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.783</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.783</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.700</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>2.783</t>
         </is>
       </c>
     </row>
@@ -8050,16 +7737,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -8068,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8080,10 +7767,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8097,12 +7784,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.750</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.750</t>
         </is>
       </c>
     </row>
@@ -8176,10 +7863,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
         <v>17</v>
@@ -8213,22 +7900,22 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.680</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.680</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.304</t>
+          <t>1.200</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>1.880</t>
         </is>
       </c>
     </row>
@@ -8302,13 +7989,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
@@ -8320,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -8329,32 +8016,32 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.609</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.609</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.348</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.905</t>
+          <t>1.957</t>
         </is>
       </c>
     </row>
@@ -8365,16 +8052,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -8402,45 +8089,45 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.344</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8449,127 +8136,127 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.727</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M13" t="n">
         <v>12</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.708</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.708</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1.083</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.948</t>
+          <t>1.791</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -8581,61 +8268,61 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>1.211</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1.948</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8644,55 +8331,55 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.829</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.429</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8701,133 +8388,133 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.778</t>
+          <t>0.910</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -8836,61 +8523,61 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>1.778</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rich</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -8899,55 +8586,55 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>0.728</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Rich</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -8962,61 +8649,61 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.550</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.550</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.950</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -9025,97 +8712,1605 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>10</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.545</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0.545</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0.909</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1.454</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="n">
+        <v>13</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>5</v>
       </c>
+      <c r="M22" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1.307</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0000FF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.643</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.643</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.964</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.607</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.800</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2.200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M4" t="n">
+        <v>19</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.783</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.783</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.783</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baxter</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Briana</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>12</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.680</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.680</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.880</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" t="n">
+        <v>23</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>19</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.609</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.609</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.348</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.957</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>13</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.719</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.344</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>27</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.708</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.708</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1.083</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.791</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kunal</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>19</v>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.737</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.737</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1.211</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.948</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>35</v>
+      </c>
+      <c r="C15" t="n">
+        <v>35</v>
+      </c>
+      <c r="D15" t="n">
+        <v>21</v>
+      </c>
+      <c r="E15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11</v>
+      </c>
+      <c r="M15" t="n">
+        <v>16</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.829</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.429</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.455</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0.455</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>0.455</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0.910</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>18</v>
+      </c>
+      <c r="C18" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>16</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.222</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.778</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ramos</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0.455</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0.728</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rich</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>22</v>
+      </c>
+      <c r="C21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>10</v>
+      </c>
       <c r="M21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.545</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0.545</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0.909</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1.454</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="n">
+        <v>13</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" t="n">
         <v>7</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>0.615</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>0.615</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>0.692</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>1.307</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>309</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>292</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>186</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="G23" s="2" t="n">
+      <c r="B24" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H23" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I23" s="2" t="n">
+      <c r="H24" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0.637</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0.644</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>1.021</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1.665</t>
+      <c r="K24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0.631</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.638</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>1.056</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1.694</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q21"/>
+  <autoFilter ref="A1:Q22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/output/stats.xlsx
+++ b/data/output/stats.xlsx
@@ -23,6 +23,7 @@
     <sheet name="Cyclo Spring 2026 Game 1" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Cyclo Spring 2026 Game 2" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Cyclo Spring 2026 Game 3" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Cyclo Spring 2026 Game 5" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$H$3</definedName>
@@ -40,6 +41,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Cyclo Spring 2026 Game 1'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Cyclo Spring 2026 Game 2'!$A$1:$Q$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Cyclo Spring 2026 Game 3'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Cyclo Spring 2026 Game 5'!$A$1:$Q$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3516,25 +3518,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3546,29 +3548,29 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>2.250</t>
         </is>
       </c>
     </row>
@@ -3642,22 +3644,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -3672,29 +3674,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3.167</t>
+          <t>2.091</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4.167</t>
+          <t>2.818</t>
         </is>
       </c>
     </row>
@@ -3705,16 +3707,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -3735,10 +3737,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3752,12 +3754,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.750</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -3831,22 +3833,22 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" t="n">
         <v>9</v>
       </c>
-      <c r="C7" t="n">
-        <v>9</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -3861,29 +3863,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1.231</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>1.923</t>
         </is>
       </c>
     </row>
@@ -3957,16 +3959,16 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -3990,26 +3992,26 @@
         <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.429</t>
+          <t>1.727</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3.143</t>
+          <t>2.363</t>
         </is>
       </c>
     </row>
@@ -4020,59 +4022,59 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
         <v>11</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>11</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
         <v>6</v>
       </c>
-      <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.688</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.688</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.688</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.090</t>
+          <t>1.376</t>
         </is>
       </c>
     </row>
@@ -4083,16 +4085,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -4104,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4113,19 +4115,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -4135,7 +4137,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.292</t>
         </is>
       </c>
     </row>
@@ -4146,59 +4148,59 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>8</v>
       </c>
-      <c r="C12" t="n">
+      <c r="M12" t="n">
         <v>7</v>
       </c>
-      <c r="D12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.909</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.179</t>
+          <t>2.469</t>
         </is>
       </c>
     </row>
@@ -4272,25 +4274,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="n">
         <v>6</v>
       </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -4302,29 +4304,29 @@
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1.437</t>
         </is>
       </c>
     </row>
@@ -4335,19 +4337,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4365,29 +4367,29 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -4398,16 +4400,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -4416,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -4425,32 +4427,32 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.462</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.462</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>1.154</t>
         </is>
       </c>
     </row>
@@ -4461,59 +4463,59 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D18" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>64</v>
-      </c>
       <c r="E18" s="2" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>0.688</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>0.687</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1.214</t>
+          <t>1.208</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>1.860</t>
+          <t>1.895</t>
         </is>
       </c>
     </row>
@@ -7220,6 +7222,884 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.400</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.400</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.800</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Baxter</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.250</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0.761</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.761</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1.196</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1.957</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7293,29 +8173,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>0.648</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>0.655</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1.074</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.694</t>
+          <t>1.729</t>
         </is>
       </c>
     </row>
@@ -7331,29 +8211,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>21</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>0.648</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>0.655</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1.074</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.694</t>
+          <t>1.729</t>
         </is>
       </c>
     </row>
@@ -7485,59 +8365,59 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>7</v>
-      </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>0.688</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>0.688</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.964</t>
+          <t>1.094</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.607</t>
+          <t>1.782</t>
         </is>
       </c>
     </row>
@@ -7611,22 +8491,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
@@ -7641,29 +8521,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.786</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.783</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -7737,16 +8617,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -7767,10 +8647,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -7784,12 +8664,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.750</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -7863,22 +8743,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -7893,29 +8773,29 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.724</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.724</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.241</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.880</t>
+          <t>1.965</t>
         </is>
       </c>
     </row>
@@ -7989,16 +8869,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -8022,26 +8902,26 @@
         <v>19</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.348</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.957</t>
+          <t>1.815</t>
         </is>
       </c>
     </row>
@@ -8052,16 +8932,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -8082,29 +8962,29 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>14</v>
+      </c>
+      <c r="M11" t="n">
         <v>13</v>
       </c>
-      <c r="M11" t="n">
-        <v>10</v>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.676</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.676</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1.433</t>
         </is>
       </c>
     </row>
@@ -8115,16 +8995,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -8136,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -8145,19 +9025,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -8167,7 +9047,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.167</t>
         </is>
       </c>
     </row>
@@ -8178,59 +9058,59 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
         <v>17</v>
       </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>13</v>
-      </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>1.214</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.791</t>
+          <t>1.964</t>
         </is>
       </c>
     </row>
@@ -8304,25 +9184,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8334,10 +9214,10 @@
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -8351,12 +9231,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>0.900</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -8430,19 +9310,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -8460,29 +9340,29 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.910</t>
+          <t>1.133</t>
         </is>
       </c>
     </row>
@@ -8682,16 +9562,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
@@ -8700,7 +9580,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -8709,32 +9589,32 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.538</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.538</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.962</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -8930,59 +9810,59 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>7</v>
-      </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>0.688</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>0.688</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.964</t>
+          <t>1.094</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.607</t>
+          <t>1.782</t>
         </is>
       </c>
     </row>
@@ -9056,22 +9936,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
@@ -9086,29 +9966,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.786</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.783</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -9182,16 +10062,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -9212,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -9229,12 +10109,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.750</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -9308,22 +10188,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -9338,29 +10218,29 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.724</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.724</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.241</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.880</t>
+          <t>1.965</t>
         </is>
       </c>
     </row>
@@ -9434,16 +10314,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -9467,26 +10347,26 @@
         <v>19</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.348</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.957</t>
+          <t>1.815</t>
         </is>
       </c>
     </row>
@@ -9497,16 +10377,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -9527,29 +10407,29 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>14</v>
+      </c>
+      <c r="M11" t="n">
         <v>13</v>
       </c>
-      <c r="M11" t="n">
-        <v>10</v>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.676</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.676</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1.433</t>
         </is>
       </c>
     </row>
@@ -9560,16 +10440,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -9581,7 +10461,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -9590,19 +10470,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -9612,7 +10492,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.167</t>
         </is>
       </c>
     </row>
@@ -9623,59 +10503,59 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
         <v>17</v>
       </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>13</v>
-      </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>1.214</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.791</t>
+          <t>1.964</t>
         </is>
       </c>
     </row>
@@ -9749,25 +10629,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -9779,10 +10659,10 @@
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -9796,12 +10676,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>0.900</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -9875,19 +10755,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -9905,29 +10785,29 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.910</t>
+          <t>1.133</t>
         </is>
       </c>
     </row>
@@ -10127,16 +11007,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
@@ -10145,7 +11025,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -10154,32 +11034,32 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.538</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.538</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.962</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -10253,59 +11133,59 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>337</v>
+        <v>385</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>320</v>
+        <v>366</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>0.648</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>0.655</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1.074</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>1.694</t>
+          <t>1.729</t>
         </is>
       </c>
     </row>

--- a/data/output/stats.xlsx
+++ b/data/output/stats.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Legend" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="League Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Player Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cyclo Total" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cyclo Spring 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cyclo Spring 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cyclo Spring 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cyclo Spring 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Cyclo Spring 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cyclo Spring 2026 Game 5" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Cyclo Spring 2026 Game 6" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Cyclo Winter 2026 Total" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Cyclo Winter 2026 Game 1" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Cyclo Winter 2026 Game 2" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Cyclo Winter 2026 Game 3" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Cyclo Winter 2026 Game 4" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Cyclo Winter 2026 Game 5" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Cyclo Winter 2026 Game 6" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Cyclo Winter 2026 Game 7" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="League Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Total" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 5" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 6" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 8" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 7" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Total" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 1" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 2" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 3" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 4" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 5" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 6" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 7" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$H$3</definedName>
@@ -38,14 +40,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cyclo Spring 2026 Game 4'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Spring 2026 Game 5'!$A$1:$Q$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Spring 2026 Game 6'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Winter 2026 Total'!$A$1:$Q$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cyclo Winter 2026 Game 1'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Cyclo Winter 2026 Game 2'!$A$1:$Q$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Cyclo Winter 2026 Game 3'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Cyclo Winter 2026 Game 4'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Cyclo Winter 2026 Game 5'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Cyclo Winter 2026 Game 6'!$A$1:$Q$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Cyclo Winter 2026 Game 7'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Spring 2026 Game 8'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cyclo Spring 2026 Game 7'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Cyclo Winter 2026 Total'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Cyclo Winter 2026 Game 1'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Cyclo Winter 2026 Game 2'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Cyclo Winter 2026 Game 3'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Cyclo Winter 2026 Game 4'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Cyclo Winter 2026 Game 5'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Cyclo Winter 2026 Game 6'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Cyclo Winter 2026 Game 7'!$A$1:$Q$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2524,11 +2528,11 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF00FF00"/>
+    <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2644,59 +2648,59 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.850</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.666</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2725,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2737,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -2754,12 +2758,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -2770,28 +2774,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2800,43 +2804,43 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.338</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -2863,29 +2867,29 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -2896,59 +2900,59 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
@@ -2959,28 +2963,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2989,29 +2993,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -3022,22 +3026,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -3052,10 +3056,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3064,40 +3068,40 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -3106,70 +3110,70 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3178,29 +3182,29 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.176</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.941</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -3211,66 +3215,66 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10</v>
-      </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.542</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3280,13 +3284,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3304,1358 +3308,165 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>5</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.444</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.455</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0.444</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>0.899</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Rafael</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>18</v>
-      </c>
-      <c r="C14" t="n">
-        <v>18</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="I15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>6</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>16</v>
-      </c>
-      <c r="M14" t="n">
-        <v>7</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>1.222</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.778</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ramos</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C15" t="n">
-        <v>11</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0.429</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0.455</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0.884</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Rich</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" t="n">
-        <v>13</v>
-      </c>
-      <c r="D17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>9</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>1.231</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1.846</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" t="n">
-        <v>13</v>
-      </c>
-      <c r="D18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E18" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>7</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>0.692</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1.359</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TEAM TOTALS</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>238</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H20" s="2" t="n">
+      <c r="M15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0.622</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0.634</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0.986</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1.620</t>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0.469</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.469</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>0.906</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>1.375</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q18"/>
+  <autoFilter ref="A1:Q13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>HRO</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>RBI</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>OBP</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>SLG</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.333</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2.333</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anthony</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.333</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bryce</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cory</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0.666</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Devon</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>1.250</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Kap</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0.666</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Kunal</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.334</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Kyla</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1.750</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Rafael</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.666</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ramos</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1.333</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TEAM TOTALS</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0.543</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0.543</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1.343</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:Q12"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -4781,13 +3592,13 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -4802,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -4811,40 +3622,40 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -4862,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4871,40 +3682,40 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
@@ -4913,19 +3724,19 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4934,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
@@ -4951,44 +3762,44 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>4.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4997,52 +3808,52 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.667</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.334</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -5051,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -5060,43 +3871,43 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -5114,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -5123,55 +3934,55 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -5186,52 +3997,52 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5249,10 +4060,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -5266,32 +4077,32 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5303,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -5312,10 +4123,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5341,23 +4152,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -5366,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -5375,36 +4186,36 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5414,13 +4225,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -5438,61 +4249,61 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -5504,21 +4315,21 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -5534,64 +4345,1320 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>1.357</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF00FF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.650</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.619</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.850</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.469</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="n">
+        <v>13</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1.588</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.338</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1.250</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.956</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.562</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.588</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.875</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.463</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>22</v>
+      </c>
+      <c r="C8" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.682</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.492</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C9" t="n">
+        <v>17</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.647</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.684</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.941</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.625</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kunal</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.765</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.765</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.176</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.941</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.917</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.542</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.455</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.899</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>18</v>
+      </c>
+      <c r="C14" t="n">
+        <v>18</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>16</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1.222</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.778</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ramos</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.429</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.455</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rich</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1.231</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1.846</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.359</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0.622</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0.986</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1.620</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5719,16 +5786,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -5749,29 +5816,29 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
@@ -5782,19 +5849,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -5812,29 +5879,29 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -5848,13 +5915,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -5863,41 +5930,41 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2.333</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3.333</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -5914,19 +5981,19 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5938,29 +6005,29 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.667</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
@@ -5971,22 +6038,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -6001,29 +6068,29 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -6061,13 +6128,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -6103,10 +6170,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -6130,26 +6197,26 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -6160,19 +6227,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -6193,26 +6260,26 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.750</t>
         </is>
       </c>
     </row>
@@ -6223,19 +6290,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -6256,26 +6323,26 @@
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
@@ -6286,16 +6353,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6319,33 +6386,33 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6355,13 +6422,13 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -6379,29 +6446,29 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -6415,56 +6482,56 @@
         <v>36</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.543</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.543</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.343</t>
         </is>
       </c>
     </row>
@@ -6475,6 +6542,1825 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kunal</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.333</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0.875</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.875</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>2.250</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.250</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.333</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3.333</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2.667</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kunal</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ramos</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0.833</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1.333</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -7289,7 +9175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -8104,7 +9990,150 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>League</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Games Played</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total Players</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Team BA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Team OBP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Team SLG</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Team OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fray</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cyclones</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.618</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.629</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.032</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.661</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fray</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cyclones</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.618</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.629</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.032</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.661</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -9045,7 +11074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -9919,149 +11948,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Q12"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>League</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Games Played</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Players</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Team BA</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Team OBP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Team SLG</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Team OPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Fray</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Cyclones</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.637</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.646</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1.053</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1.699</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Fray</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Cyclones</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>13</v>
-      </c>
-      <c r="D3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.637</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.646</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1.053</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.699</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10188,13 +12074,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
         <v>18</v>
@@ -10206,41 +12092,41 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.128</t>
+          <t>1.091</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.872</t>
+          <t>1.773</t>
         </is>
       </c>
     </row>
@@ -10251,25 +12137,25 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
         <v>10</v>
-      </c>
-      <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -10281,29 +12167,29 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>2.143</t>
         </is>
       </c>
     </row>
@@ -10314,13 +12200,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
@@ -10329,13 +12215,13 @@
         <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -10344,29 +12230,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>0.725</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>0.725</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.857</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -10440,59 +12326,59 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>21</v>
+      </c>
+      <c r="C6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" t="n">
         <v>15</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6" t="n">
-        <v>13</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>10</v>
-      </c>
-      <c r="M6" t="n">
-        <v>12</v>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>2.191</t>
         </is>
       </c>
     </row>
@@ -10566,16 +12452,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -10596,29 +12482,29 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.634</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.634</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>1.049</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.857</t>
+          <t>1.683</t>
         </is>
       </c>
     </row>
@@ -10692,16 +12578,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -10722,29 +12608,29 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.639</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.639</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>1.194</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.833</t>
         </is>
       </c>
     </row>
@@ -10755,16 +12641,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C11" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -10776,7 +12662,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -10785,29 +12671,29 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M11" t="n">
         <v>15</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>0.627</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>0.627</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.313</t>
         </is>
       </c>
     </row>
@@ -10818,16 +12704,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -10851,16 +12737,16 @@
         <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.450</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.450</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -10870,7 +12756,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>0.950</t>
         </is>
       </c>
     </row>
@@ -10881,19 +12767,19 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>43</v>
+      </c>
+      <c r="C13" t="n">
         <v>38</v>
       </c>
-      <c r="C13" t="n">
-        <v>35</v>
-      </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -10902,7 +12788,7 @@
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -10914,26 +12800,26 @@
         <v>20</v>
       </c>
       <c r="M13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.029</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -11007,13 +12893,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" t="n">
         <v>18</v>
@@ -11025,10 +12911,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -11037,29 +12923,29 @@
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>0.821</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.307</t>
+          <t>1.321</t>
         </is>
       </c>
     </row>
@@ -11133,59 +13019,59 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
         <v>10</v>
       </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6</v>
-      </c>
-      <c r="M17" t="n">
-        <v>8</v>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>1.120</t>
         </is>
       </c>
     </row>
@@ -11385,22 +13271,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
@@ -11415,29 +13301,29 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>0.972</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.437</t>
+          <t>1.528</t>
         </is>
       </c>
     </row>
@@ -11633,13 +13519,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
         <v>18</v>
@@ -11651,41 +13537,41 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.128</t>
+          <t>1.091</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.872</t>
+          <t>1.773</t>
         </is>
       </c>
     </row>
@@ -11696,25 +13582,25 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
         <v>10</v>
-      </c>
-      <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -11726,29 +13612,29 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>2.143</t>
         </is>
       </c>
     </row>
@@ -11759,13 +13645,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
@@ -11774,13 +13660,13 @@
         <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -11789,29 +13675,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>0.725</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>0.725</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.857</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -11885,59 +13771,59 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>21</v>
+      </c>
+      <c r="C6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" t="n">
         <v>15</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6" t="n">
-        <v>13</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>10</v>
-      </c>
-      <c r="M6" t="n">
-        <v>12</v>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>2.191</t>
         </is>
       </c>
     </row>
@@ -12011,16 +13897,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -12041,29 +13927,29 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.634</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.634</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>1.049</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.857</t>
+          <t>1.683</t>
         </is>
       </c>
     </row>
@@ -12137,16 +14023,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -12167,29 +14053,29 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.639</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.639</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>1.194</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.833</t>
         </is>
       </c>
     </row>
@@ -12200,16 +14086,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C11" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -12221,7 +14107,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -12230,29 +14116,29 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M11" t="n">
         <v>15</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>0.627</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>0.627</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.313</t>
         </is>
       </c>
     </row>
@@ -12263,16 +14149,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -12296,16 +14182,16 @@
         <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.450</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.450</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -12315,7 +14201,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>0.950</t>
         </is>
       </c>
     </row>
@@ -12326,19 +14212,19 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>43</v>
+      </c>
+      <c r="C13" t="n">
         <v>38</v>
       </c>
-      <c r="C13" t="n">
-        <v>35</v>
-      </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -12347,7 +14233,7 @@
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -12359,26 +14245,26 @@
         <v>20</v>
       </c>
       <c r="M13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.029</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -12452,13 +14338,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" t="n">
         <v>18</v>
@@ -12470,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -12482,29 +14368,29 @@
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>0.821</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.307</t>
+          <t>1.321</t>
         </is>
       </c>
     </row>
@@ -12578,59 +14464,59 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
         <v>10</v>
       </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6</v>
-      </c>
-      <c r="M17" t="n">
-        <v>8</v>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>1.120</t>
         </is>
       </c>
     </row>
@@ -12830,22 +14716,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
@@ -12860,29 +14746,29 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>0.972</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.437</t>
+          <t>1.528</t>
         </is>
       </c>
     </row>
@@ -12956,59 +14842,59 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>460</v>
+        <v>526</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>438</v>
+        <v>498</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>7</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>0.618</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>0.629</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1.053</t>
+          <t>1.032</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>1.661</t>
         </is>
       </c>
     </row>
@@ -13141,13 +15027,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
         <v>9</v>
@@ -13159,41 +15045,41 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M2" t="n">
         <v>11</v>
       </c>
-      <c r="M2" t="n">
-        <v>10</v>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>0.708</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>0.680</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>1.292</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.263</t>
+          <t>1.972</t>
         </is>
       </c>
     </row>
@@ -13204,25 +15090,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -13234,29 +15120,29 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
@@ -13267,13 +15153,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -13282,13 +15168,13 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -13297,29 +15183,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.739</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.111</t>
+          <t>1.913</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.944</t>
+          <t>2.663</t>
         </is>
       </c>
     </row>
@@ -13330,59 +15216,59 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M5" t="n">
         <v>15</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>13</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M5" t="n">
-        <v>12</v>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>2.191</t>
         </is>
       </c>
     </row>
@@ -13456,16 +15342,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -13486,29 +15372,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>0.560</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>0.577</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>0.920</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.497</t>
         </is>
       </c>
     </row>
@@ -13582,16 +15468,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -13612,29 +15498,29 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>0.700</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.450</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.331</t>
+          <t>2.164</t>
         </is>
       </c>
     </row>
@@ -13645,59 +15531,59 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>14</v>
-      </c>
-      <c r="E10" t="n">
-        <v>14</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>0.613</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.166</t>
+          <t>1.213</t>
         </is>
       </c>
     </row>
@@ -13708,16 +15594,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -13741,11 +15627,11 @@
         <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.450</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -13771,19 +15657,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -13792,7 +15678,7 @@
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -13804,26 +15690,26 @@
         <v>11</v>
       </c>
       <c r="M12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.789</t>
+          <t>0.792</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>1.524</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.400</t>
+          <t>2.316</t>
         </is>
       </c>
     </row>
@@ -13897,13 +15783,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
         <v>8</v>
@@ -13915,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -13927,29 +15813,29 @@
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.440</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.440</t>
+          <t>0.424</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.080</t>
+          <t>1.174</t>
         </is>
       </c>
     </row>
@@ -13960,16 +15846,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -13990,29 +15876,29 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.588</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.688</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.276</t>
         </is>
       </c>
     </row>
@@ -14023,22 +15909,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -14053,29 +15939,29 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>0.826</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1.348</t>
         </is>
       </c>
     </row>
@@ -14086,59 +15972,59 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>222</v>
+        <v>288</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>216</v>
+        <v>276</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>6</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>0.616</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1.120</t>
+          <t>1.069</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>1.778</t>
+          <t>1.694</t>
         </is>
       </c>
     </row>

--- a/data/output/stats.xlsx
+++ b/data/output/stats.xlsx
@@ -1,38 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="League Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Total" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 5" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 6" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 8" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Spring 2026 Game 7" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Total" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 1" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 2" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 3" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 4" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 5" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 6" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyclo Winter 2026 Game 7" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Legend" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="League Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Player Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cyclo Total" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cyclo Spring 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cyclo Spring 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cyclo Spring 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cyclo Spring 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cyclo Spring 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cyclo Spring 2026 Game 5" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Cyclo Spring 2026 Game 6" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Cyclo Spring 2026 Game 7" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Cyclo Spring 2026 Game 8" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Cyclo Winter 2026 Total" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Cyclo Winter 2026 Game 1" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Cyclo Winter 2026 Game 2" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Cyclo Winter 2026 Game 3" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Cyclo Winter 2026 Game 4" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Cyclo Winter 2026 Game 5" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Cyclo Winter 2026 Game 6" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Cyclo Winter 2026 Game 7" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Cyclo Summer 2026 Total" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Cyclo Summer 2026 Game 1" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$H$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cyclo Total'!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cyclo Total'!$A$1:$Q$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cyclo Spring 2026 Total'!$A$1:$Q$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Spring 2026 Game 1'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Spring 2026 Game 2'!$A$1:$Q$13</definedName>
@@ -40,8 +42,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cyclo Spring 2026 Game 4'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Spring 2026 Game 5'!$A$1:$Q$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Spring 2026 Game 6'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Spring 2026 Game 8'!$A$1:$Q$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cyclo Spring 2026 Game 7'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Spring 2026 Game 7'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cyclo Spring 2026 Game 8'!$A$1:$Q$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Cyclo Winter 2026 Total'!$A$1:$Q$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Cyclo Winter 2026 Game 1'!$A$1:$Q$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Cyclo Winter 2026 Game 2'!$A$1:$Q$13</definedName>
@@ -50,6 +52,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Cyclo Winter 2026 Game 5'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Cyclo Winter 2026 Game 6'!$A$1:$Q$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Cyclo Winter 2026 Game 7'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Cyclo Summer 2026 Total'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Cyclo Summer 2026 Game 1'!$A$1:$Q$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2651,10 +2655,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2666,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -2681,26 +2685,26 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -2723,13 +2727,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2741,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -2758,12 +2762,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -2777,10 +2781,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2789,13 +2793,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2804,29 +2808,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>4.000</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2850,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2855,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2867,10 +2871,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2884,12 +2888,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.667</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>2.334</t>
         </is>
       </c>
     </row>
@@ -2930,10 +2934,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2969,10 +2973,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2993,29 +2997,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -3026,37 +3030,37 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -3095,10 +3099,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -3122,26 +3126,26 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -3152,19 +3156,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3189,12 +3193,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -3204,7 +3208,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -3218,10 +3222,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3233,10 +3237,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -3245,29 +3249,29 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -3284,10 +3288,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -3308,29 +3312,29 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -3347,16 +3351,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -3371,19 +3375,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3393,7 +3397,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -3404,59 +3408,59 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.357</t>
         </is>
       </c>
     </row>
@@ -3592,10 +3596,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3607,13 +3611,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -3622,26 +3626,26 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.666</t>
         </is>
       </c>
     </row>
@@ -3664,13 +3668,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -3682,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -3699,12 +3703,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -3718,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3730,13 +3734,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3745,29 +3749,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3791,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -3796,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3808,10 +3812,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3825,12 +3829,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -3871,10 +3875,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3910,10 +3914,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3934,29 +3938,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3971,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
@@ -3988,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3997,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -4036,10 +4040,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -4063,26 +4067,26 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -4093,19 +4097,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4130,22 +4134,22 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4163,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4174,10 +4178,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4186,29 +4190,29 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -4225,10 +4229,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -4249,29 +4253,29 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
@@ -4288,16 +4292,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4312,19 +4316,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -4334,7 +4338,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -4345,59 +4349,59 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>28</v>
-      </c>
       <c r="D15" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.469</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.469</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.906</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1.375</t>
         </is>
       </c>
     </row>
@@ -9996,7 +10000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10063,72 +10067,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>0.631</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1.021</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.661</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Fray</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Cyclones</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.618</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.629</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1.032</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.661</t>
+          <t>1.652</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11952,13 +11918,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF00FF00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12074,59 +12041,59 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.773</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
@@ -12137,25 +12104,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -12164,64 +12131,64 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.143</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -12230,49 +12197,49 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>0.333</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -12284,7 +12251,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -12300,54 +12267,54 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>0.500</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.833</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -12356,49 +12323,49 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.191</t>
+          <t>1.167</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Briana</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -12422,112 +12389,112 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.049</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.683</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -12536,7 +12503,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -12545,58 +12512,58 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -12605,55 +12572,55 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.194</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -12662,7 +12629,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -12671,735 +12638,1045 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>8</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.450</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.450</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.950</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Kap</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>43</v>
-      </c>
-      <c r="C13" t="n">
-        <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>28</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>20</v>
-      </c>
-      <c r="M13" t="n">
-        <v>19</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>1.263</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Kunal</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>19</v>
-      </c>
-      <c r="C14" t="n">
-        <v>19</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="M14" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E14" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>8</v>
-      </c>
-      <c r="M14" t="n">
-        <v>12</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>1.211</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.948</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Kyla</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>57</v>
-      </c>
-      <c r="C15" t="n">
-        <v>56</v>
-      </c>
-      <c r="D15" t="n">
-        <v>28</v>
-      </c>
-      <c r="E15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>20</v>
-      </c>
-      <c r="M15" t="n">
-        <v>21</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0.821</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1.321</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Kyle</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>28</v>
-      </c>
-      <c r="C17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>13</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" t="n">
-        <v>10</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>0.520</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0.520</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1.120</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Rafael</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>18</v>
-      </c>
-      <c r="C18" t="n">
-        <v>18</v>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>16</v>
-      </c>
-      <c r="M18" t="n">
-        <v>7</v>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0.556</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>1.222</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1.778</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ramos</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C19" t="n">
-        <v>11</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>0.455</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>0.728</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Rich</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>36</v>
-      </c>
-      <c r="C21" t="n">
-        <v>36</v>
-      </c>
-      <c r="D21" t="n">
-        <v>20</v>
-      </c>
-      <c r="E21" t="n">
-        <v>11</v>
-      </c>
-      <c r="F21" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>14</v>
-      </c>
-      <c r="M21" t="n">
-        <v>18</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>0.972</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1.528</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>15</v>
-      </c>
-      <c r="C22" t="n">
-        <v>13</v>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>7</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>0.692</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>1.307</t>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.657</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0.815</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1.472</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q22"/>
+  <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF0000FF"/>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1.333</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2.333</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pete</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.333</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0.815</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1.371</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13519,19 +13796,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -13549,29 +13826,29 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.702</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.702</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>1.106</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.773</t>
+          <t>1.808</t>
         </is>
       </c>
     </row>
@@ -13582,59 +13859,59 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>20</v>
+      </c>
+      <c r="M3" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>17</v>
-      </c>
-      <c r="M3" t="n">
-        <v>8</v>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.294</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.143</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -14023,10 +14300,10 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>41</v>
+      </c>
+      <c r="C10" t="n">
         <v>38</v>
-      </c>
-      <c r="C10" t="n">
-        <v>36</v>
       </c>
       <c r="D10" t="n">
         <v>23</v>
@@ -14044,7 +14321,7 @@
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -14060,22 +14337,22 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>0.605</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>0.605</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.194</t>
+          <t>1.132</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.737</t>
         </is>
       </c>
     </row>
@@ -14149,17 +14426,17 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
         <v>9</v>
       </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
@@ -14170,7 +14447,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -14179,29 +14456,29 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
         <v>8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.450</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.450</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.478</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.950</t>
+          <t>0.913</t>
         </is>
       </c>
     </row>
@@ -14212,16 +14489,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
@@ -14233,7 +14510,7 @@
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -14242,58 +14519,58 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
+        <v>21</v>
+      </c>
+      <c r="M13" t="n">
         <v>20</v>
       </c>
-      <c r="M13" t="n">
-        <v>19</v>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.725</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.725</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.225</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.950</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -14305,178 +14582,178 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.948</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>1.211</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.948</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.867</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.400</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -14485,133 +14762,133 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.520</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.520</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.120</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.538</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.538</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.778</t>
+          <t>1.192</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -14620,58 +14897,58 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rich</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -14683,223 +14960,1920 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.238</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.809</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.273</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.972</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>0.728</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Rich</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>39</v>
+      </c>
+      <c r="C23" t="n">
+        <v>38</v>
+      </c>
+      <c r="D23" t="n">
+        <v>20</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14</v>
+      </c>
+      <c r="M23" t="n">
+        <v>19</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.526</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0.526</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>0.921</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1.447</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Taylor</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" t="n">
+        <v>13</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>7</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.307</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q24"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0000FF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>19</v>
+      </c>
+      <c r="M2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.702</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.702</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1.106</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.808</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>20</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1.294</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>44</v>
+      </c>
+      <c r="C4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>24</v>
+      </c>
+      <c r="M4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.725</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.725</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baxter</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>21</v>
+      </c>
+      <c r="C6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" t="n">
+        <v>15</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1.381</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.191</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Briana</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bryce</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>43</v>
+      </c>
+      <c r="C8" t="n">
+        <v>41</v>
+      </c>
+      <c r="D8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>17</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1.049</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.683</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>41</v>
+      </c>
+      <c r="C10" t="n">
+        <v>38</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>21</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.605</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.605</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.132</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.737</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>53</v>
+      </c>
+      <c r="C11" t="n">
+        <v>51</v>
+      </c>
+      <c r="D11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>23</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.627</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.627</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.686</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.313</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.435</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.435</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.478</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.913</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kap</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>46</v>
+      </c>
+      <c r="C13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D13" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.725</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.725</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1.225</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.950</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kunal</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>19</v>
+      </c>
+      <c r="C15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>12</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.737</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.737</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1.211</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.948</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kyla</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>61</v>
+      </c>
+      <c r="C16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D16" t="n">
+        <v>32</v>
+      </c>
+      <c r="E16" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23</v>
+      </c>
+      <c r="M16" t="n">
+        <v>24</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.533</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.533</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0.867</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>31</v>
+      </c>
+      <c r="C18" t="n">
+        <v>26</v>
+      </c>
+      <c r="D18" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.538</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.538</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.654</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.192</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pete</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>21</v>
+      </c>
+      <c r="C20" t="n">
+        <v>21</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1.238</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1.809</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ramos</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="n">
+        <v>11</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0.455</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>0.728</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rich</t>
+        </is>
+      </c>
       <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>39</v>
+      </c>
+      <c r="C23" t="n">
+        <v>38</v>
+      </c>
+      <c r="D23" t="n">
+        <v>20</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14</v>
+      </c>
+      <c r="M23" t="n">
+        <v>19</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.526</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0.526</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>0.921</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1.447</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>15</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C24" t="n">
         <v>13</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D24" t="n">
         <v>8</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E24" t="n">
         <v>7</v>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M24" t="n">
         <v>7</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>0.615</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>0.615</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>0.692</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>1.307</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>526</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>498</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>308</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H24" s="2" t="n">
+      <c r="B26" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>525</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H26" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J24" s="2" t="n">
+      <c r="I26" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="J26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K26" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L24" s="2" t="n">
-        <v>231</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>231</v>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0.618</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0.629</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>1.032</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1.661</t>
+      <c r="L26" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.631</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1.021</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1.652</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q22"/>
+  <autoFilter ref="A1:Q24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/output/stats.xlsx
+++ b/data/output/stats.xlsx
@@ -10167,12 +10167,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.997</t>
+          <t>0.996</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.618</t>
         </is>
       </c>
     </row>
@@ -20479,10 +20479,10 @@
         <v>39</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -20517,12 +20517,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1.170</t>
+          <t>1.151</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.916</t>
+          <t>1.897</t>
         </is>
       </c>
     </row>
@@ -25688,10 +25688,10 @@
         <v>39</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -25726,12 +25726,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1.170</t>
+          <t>1.151</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.916</t>
+          <t>1.897</t>
         </is>
       </c>
     </row>
@@ -26507,10 +26507,10 @@
         <v>486</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>24</v>
@@ -26545,12 +26545,12 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0.997</t>
+          <t>0.996</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.618</t>
         </is>
       </c>
     </row>
@@ -27259,10 +27259,10 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -27297,12 +27297,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -27637,10 +27637,10 @@
         <v>42</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>2</v>
@@ -27675,12 +27675,12 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>1.172</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>1.830</t>
+          <t>1.814</t>
         </is>
       </c>
     </row>
@@ -29078,10 +29078,10 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -29116,12 +29116,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -29330,10 +29330,10 @@
         <v>16</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -29368,12 +29368,12 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1.034</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.552</t>
         </is>
       </c>
     </row>

--- a/data/output/stats.xlsx
+++ b/data/output/stats.xlsx
@@ -45,7 +45,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cyclo Total'!$A$1:$Q$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cyclo Late Summer 2026 Total'!$A$1:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cyclo Late Summer 2026 Total'!$A$1:$Q$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Late Summer 2026 Game 1'!$A$1:$Q$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Late Summer 2026 Game 2'!$A$1:$Q$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cyclo Summer 2026 Total'!$A$1:$Q$18</definedName>
@@ -20722,16 +20722,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C19" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -20746,35 +20746,35 @@
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M19" t="n">
         <v>36</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.849</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1.442</t>
         </is>
       </c>
     </row>
@@ -20785,16 +20785,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -20809,35 +20809,35 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.300</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -25931,16 +25931,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C19" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -25955,35 +25955,35 @@
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M19" t="n">
         <v>36</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>0.849</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1.442</t>
         </is>
       </c>
     </row>
@@ -25994,16 +25994,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -26018,35 +26018,35 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.300</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -26567,7 +26567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27313,82 +27313,82 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="n">
         <v>6</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>6</v>
       </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4</v>
-      </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.378</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -27400,7 +27400,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -27409,55 +27409,55 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -27469,10 +27469,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -27486,32 +27486,32 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>3.500</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -27535,157 +27535,94 @@
         <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.200</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>3.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>1.200</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
           <t>1.800</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C17" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D17" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="2" t="n">
+      <c r="G17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="2" t="n">
+      <c r="I17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0.656</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0.642</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>1.172</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1.814</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q16"/>
+  <autoFilter ref="A1:Q15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29128,7 +29065,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B11" t="n">
